--- a/tasks/finalpool/yt-12306-tech-conference-travel-notion-excel/groundtruth_workspace/Tech_Conference_Plan.xlsx
+++ b/tasks/finalpool/yt-12306-tech-conference-travel-notion-excel/groundtruth_workspace/Tech_Conference_Plan.xlsx
@@ -456,23 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TypeScript 5.0 is Here</t>
+          <t>Big Tech in panic mode... Did DeepSeek R1 just pop the AI bubble?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3200000</v>
+        <v>3878491</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TypeScript, JavaScript, Type System</t>
+          <t>AI, DeepSeek, LLM</t>
         </is>
       </c>
     </row>
@@ -482,23 +482,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>React Server Components in 100 Seconds</t>
+          <t>This free Chinese AI just crushed OpenAI's $200 o1 model...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2800000</v>
+        <v>3115193</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>React, Next.js, Server Components</t>
+          <t>AI, OpenAI, LLM</t>
         </is>
       </c>
     </row>
@@ -508,23 +508,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bun is Way Faster Than Node.js</t>
+          <t>100+ Linux Things you Need to Know</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bun</t>
+          <t>Systems</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2500000</v>
+        <v>2891861</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>12.4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bun, Node.js, JavaScript Runtime</t>
+          <t>Linux, Systems, Operating System</t>
         </is>
       </c>
     </row>
@@ -534,23 +534,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI Code Assistants Are Getting Scary Good</t>
+          <t>25 crazy software bugs explained</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2100000</v>
+        <v>2496715</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>16.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AI, Copilot, Code Generation</t>
+          <t>Bugs, Software, Engineering</t>
         </is>
       </c>
     </row>
@@ -560,23 +560,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Docker in 100 Seconds</t>
+          <t>Some bad code just broke a billion Windows machines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1900000</v>
+        <v>2467547</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Docker, Containers, DevOps</t>
+          <t>Windows, DevOps, Outage</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>北京南</t>
+          <t>Beijing South</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>曲阜东</t>
+          <t>Qufu East</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,11 +677,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>一等座</t>
+          <t>First Class</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>253</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="3">
@@ -697,12 +697,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>曲阜东</t>
+          <t>Qufu East</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>北京南</t>
+          <t>Beijing South</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -720,11 +720,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>一等座</t>
+          <t>First Class</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>253</v>
+        <v>174.5</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +781,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Depart Beijing South on G235</t>
+          <t>Depart Beijing South</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Arrive Qufu East 19:16</t>
+          <t>Outbound train to Qufu</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Registration at 08:30</t>
+          <t>Registration starts at 08:30</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Choose from track A or B</t>
+          <t>Choose track A or B</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Optional dinner event</t>
+          <t>Optional dinner</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Depart Qufu East on G236</t>
+          <t>Depart Qufu East</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arrive Beijing South 16:46</t>
+          <t>Return train to Beijing</t>
         </is>
       </c>
     </row>

--- a/tasks/finalpool/yt-12306-tech-conference-travel-notion-excel/groundtruth_workspace/Tech_Conference_Plan.xlsx
+++ b/tasks/finalpool/yt-12306-tech-conference-travel-notion-excel/groundtruth_workspace/Tech_Conference_Plan.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beijing South</t>
+          <t>北京南</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Qufu East</t>
+          <t>曲阜东</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>First Class</t>
+          <t>一等座</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -697,12 +697,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Qufu East</t>
+          <t>曲阜东</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Beijing South</t>
+          <t>北京南</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>First Class</t>
+          <t>一等座</t>
         </is>
       </c>
       <c r="I3" t="n">
